--- a/projeto_horto/conecta/static/conecta/files/Calendario.xlsx
+++ b/projeto_horto/conecta/static/conecta/files/Calendario.xlsx
@@ -27,18 +27,12 @@
     <t>Sim</t>
   </si>
   <si>
-    <t>Noções Básica I</t>
-  </si>
-  <si>
     <t>1 Introdução ao Hardware e Software</t>
   </si>
   <si>
     <t>—</t>
   </si>
   <si>
-    <t>Noções Básica II</t>
-  </si>
-  <si>
     <t>Não</t>
   </si>
   <si>
@@ -48,33 +42,12 @@
     <t>Feriado: Sexta-feira Santa</t>
   </si>
   <si>
-    <t>Power Point I</t>
-  </si>
-  <si>
     <t>2 Pacote Office</t>
   </si>
   <si>
-    <t>Power Point II / Canvas</t>
-  </si>
-  <si>
-    <t>Excel I</t>
-  </si>
-  <si>
     <t>Feriado: Dia do Trabalho (01/05)</t>
   </si>
   <si>
-    <t>Excel II</t>
-  </si>
-  <si>
-    <t>Excel III</t>
-  </si>
-  <si>
-    <t>Ferramentas Google</t>
-  </si>
-  <si>
-    <t>IA / Browser</t>
-  </si>
-  <si>
     <t>Feriado: Corpus Christi</t>
   </si>
   <si>
@@ -129,9 +102,6 @@
     <t>27/06/2026</t>
   </si>
   <si>
-    <t>Word</t>
-  </si>
-  <si>
     <t>Professor</t>
   </si>
   <si>
@@ -175,6 +145,36 @@
   </si>
   <si>
     <t>Thiago / Gilmar</t>
+  </si>
+  <si>
+    <t>Aula 10: Ferramentas Google</t>
+  </si>
+  <si>
+    <t>Aula 11: IA / Browser</t>
+  </si>
+  <si>
+    <t>Aula 08: Excel III</t>
+  </si>
+  <si>
+    <t>Aula 07: Excel II</t>
+  </si>
+  <si>
+    <t>Aula 06: Excel I</t>
+  </si>
+  <si>
+    <t>Aula 05: Power Point II / Canvas</t>
+  </si>
+  <si>
+    <t>Aula 04: Power Point I</t>
+  </si>
+  <si>
+    <t>Aula 03: Word</t>
+  </si>
+  <si>
+    <t>Aula 02: Noções Básica II</t>
+  </si>
+  <si>
+    <t>Aula 01: Noções Básica I</t>
   </si>
 </sst>
 </file>
@@ -552,19 +552,20 @@
   <dimension ref="A1:F16"/>
   <sheetFormatPr defaultColWidth="43.6640625" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="18.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.77734375" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="47.5546875" customWidth="1"/>
+    <col min="1" max="1" width="14.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="44.6640625" customWidth="1"/>
+    <col min="4" max="4" width="44.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.44140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="38.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="17.399999999999999">
       <c r="A1" s="1" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>0</v>
@@ -573,310 +574,310 @@
         <v>1</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="17.399999999999999">
       <c r="A2" s="3" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>4</v>
-      </c>
       <c r="E2" s="2" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="17.399999999999999">
       <c r="A3" s="3" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>6</v>
+        <v>51</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="17.399999999999999">
       <c r="A4" s="3" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>7</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="17.399999999999999">
       <c r="A5" s="3" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="17.399999999999999">
       <c r="A6" s="3" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>10</v>
+        <v>49</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="17.399999999999999">
       <c r="A7" s="3" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="17.399999999999999">
       <c r="A8" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="17.399999999999999">
       <c r="A9" s="3" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>13</v>
+        <v>47</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="17.399999999999999">
       <c r="A10" s="3" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="17.399999999999999">
       <c r="A11" s="3" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="17.399999999999999">
       <c r="A12" s="3" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="17.399999999999999">
       <c r="A13" s="3" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="17.399999999999999">
       <c r="A14" s="3" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="17.399999999999999">
       <c r="A15" s="3" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="17.399999999999999">
       <c r="A16" s="3" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/projeto_horto/conecta/static/conecta/files/Calendario.xlsx
+++ b/projeto_horto/conecta/static/conecta/files/Calendario.xlsx
@@ -147,12 +147,6 @@
     <t>Thiago / Gilmar</t>
   </si>
   <si>
-    <t>Aula 10: Ferramentas Google</t>
-  </si>
-  <si>
-    <t>Aula 11: IA / Browser</t>
-  </si>
-  <si>
     <t>Aula 08: Excel III</t>
   </si>
   <si>
@@ -175,6 +169,12 @@
   </si>
   <si>
     <t>Aula 01: Noções Básica I</t>
+  </si>
+  <si>
+    <t>Aula 09: Ferramentas Google</t>
+  </si>
+  <si>
+    <t>Aula 10: IA / Browser</t>
   </si>
 </sst>
 </file>
@@ -588,7 +588,7 @@
         <v>2</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>3</v>
@@ -608,7 +608,7 @@
         <v>2</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>3</v>
@@ -648,7 +648,7 @@
         <v>2</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>8</v>
@@ -668,7 +668,7 @@
         <v>2</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>8</v>
@@ -688,7 +688,7 @@
         <v>2</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>8</v>
@@ -728,7 +728,7 @@
         <v>2</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>8</v>
@@ -748,7 +748,7 @@
         <v>2</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>8</v>
@@ -768,7 +768,7 @@
         <v>2</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>8</v>
@@ -788,7 +788,7 @@
         <v>2</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>36</v>
@@ -828,7 +828,7 @@
         <v>2</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>36</v>
